--- a/artfynd/A 61196-2022 artfynd.xlsx
+++ b/artfynd/A 61196-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61196-2022 artfynd.xlsx
+++ b/artfynd/A 61196-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73357561</v>
+        <v>73357571</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762987.8972194181</v>
+        <v>762722</v>
       </c>
       <c r="R2" t="n">
-        <v>7235867.964465811</v>
+        <v>7235641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73357560</v>
+        <v>113886453</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövmyran, Vb</t>
+          <t>Melsträsk, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763024.0250559952</v>
+        <v>763053</v>
       </c>
       <c r="R3" t="n">
-        <v>7235913.899363906</v>
+        <v>7235951</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +866,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73357559</v>
+        <v>113886454</v>
       </c>
       <c r="B4" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövmyran, Vb</t>
+          <t>Melsträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763024.0250559952</v>
+        <v>763165</v>
       </c>
       <c r="R4" t="n">
-        <v>7235913.899363906</v>
+        <v>7236083</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,49 +972,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73357562</v>
+        <v>73357561</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762996.0859519301</v>
+        <v>762988</v>
       </c>
       <c r="R5" t="n">
-        <v>7235856.853162348</v>
+        <v>7235868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1052,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73357569</v>
+        <v>113886504</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1092,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövmyran, Vb</t>
+          <t>Melsträsk, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762781.8693246655</v>
+        <v>763092</v>
       </c>
       <c r="R6" t="n">
-        <v>7235709.194216803</v>
+        <v>7235977</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1150,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73357566</v>
+        <v>73357559</v>
       </c>
       <c r="B7" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762913.9785440757</v>
+        <v>763024</v>
       </c>
       <c r="R7" t="n">
-        <v>7235827.964831056</v>
+        <v>7235914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1255,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1284,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73357557</v>
+        <v>73357555</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763187.1482407087</v>
+        <v>763257</v>
       </c>
       <c r="R8" t="n">
-        <v>7236092.956108366</v>
+        <v>7236088</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1352,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1381,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73357554</v>
+        <v>73357557</v>
       </c>
       <c r="B9" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763233.9403822476</v>
+        <v>763187</v>
       </c>
       <c r="R9" t="n">
-        <v>7236062.032681663</v>
+        <v>7236093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1449,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,19 +1478,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73357555</v>
+        <v>73357567</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763257.0084680425</v>
+        <v>762809</v>
       </c>
       <c r="R10" t="n">
-        <v>7236088.196167746</v>
+        <v>7235729</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1546,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73357568</v>
+        <v>73357569</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762808.9029448677</v>
+        <v>762782</v>
       </c>
       <c r="R11" t="n">
-        <v>7235728.942540397</v>
+        <v>7235709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1643,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1672,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73357558</v>
+        <v>73357564</v>
       </c>
       <c r="B12" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763083.8292805926</v>
+        <v>762996</v>
       </c>
       <c r="R12" t="n">
-        <v>7235983.936587916</v>
+        <v>7235857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1740,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1769,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73357564</v>
+        <v>73357562</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762996.0859519301</v>
+        <v>762996</v>
       </c>
       <c r="R13" t="n">
-        <v>7235856.853162348</v>
+        <v>7235857</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1837,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,53 +1866,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73357567</v>
+        <v>113888240</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövmyran, Vb</t>
+          <t>Melsträsk, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762808.9029448677</v>
+        <v>763015</v>
       </c>
       <c r="R14" t="n">
-        <v>7235728.942540397</v>
+        <v>7236084</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +1935,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,49 +1960,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73357565</v>
+        <v>73357556</v>
       </c>
       <c r="B15" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762940.0291302761</v>
+        <v>763187</v>
       </c>
       <c r="R15" t="n">
-        <v>7235853.969948088</v>
+        <v>7236093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2040,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,53 +2069,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73357570</v>
+        <v>113888204</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövmyran, Vb</t>
+          <t>Melsträsk, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762781.8693246655</v>
+        <v>762812</v>
       </c>
       <c r="R16" t="n">
-        <v>7235709.194216803</v>
+        <v>7235843</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2138,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,27 +2163,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113886504</v>
+        <v>73357568</v>
       </c>
       <c r="B17" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,41 +2186,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763092</v>
+        <v>762809</v>
       </c>
       <c r="R17" t="n">
-        <v>7235977</v>
+        <v>7235729</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,17 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,69 +2260,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113886453</v>
+        <v>73357570</v>
       </c>
       <c r="B18" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763053</v>
+        <v>762782</v>
       </c>
       <c r="R18" t="n">
-        <v>7235951</v>
+        <v>7235709</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2540,17 +2337,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,54 +2357,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113886584</v>
+        <v>113888160</v>
       </c>
       <c r="B19" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2621,10 +2408,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763023</v>
+        <v>763251</v>
       </c>
       <c r="R19" t="n">
-        <v>7235925</v>
+        <v>7236111</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2688,15 +2475,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113888204</v>
+        <v>73357554</v>
       </c>
       <c r="B20" t="n">
-        <v>97549</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,41 +2486,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762812</v>
+        <v>763234</v>
       </c>
       <c r="R20" t="n">
-        <v>7235843</v>
+        <v>7236062</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2762,17 +2540,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,69 +2560,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113886454</v>
+        <v>73357558</v>
       </c>
       <c r="B21" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>763165</v>
+        <v>763084</v>
       </c>
       <c r="R21" t="n">
-        <v>7236083</v>
+        <v>7235984</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,17 +2637,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,69 +2657,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113888160</v>
+        <v>73357560</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>763251</v>
+        <v>763024</v>
       </c>
       <c r="R22" t="n">
-        <v>7236111</v>
+        <v>7235914</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2984,17 +2734,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,69 +2754,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113888240</v>
+        <v>73357565</v>
       </c>
       <c r="B23" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Melsträsk, Vb</t>
+          <t>Lövmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>763015</v>
+        <v>762940</v>
       </c>
       <c r="R23" t="n">
-        <v>7236084</v>
+        <v>7235854</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3095,17 +2831,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3120,15 +2851,112 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>73357566</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lövmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>762914</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7235828</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61196-2022 artfynd.xlsx
+++ b/artfynd/A 61196-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886454</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357561</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357555</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357564</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357562</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357556</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888204</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357568</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357570</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2472,6 +2562,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888160</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2569,6 +2664,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357554</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2666,6 +2766,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357558</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2763,6 +2868,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357560</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,6 +2970,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357565</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,8 +3072,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73357566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>